--- a/data/trans_orig/P32C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265418</t>
+          <t>265540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276932</t>
+          <t>277094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178665</t>
+          <t>178045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>447997</t>
+          <t>447038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>461907</t>
+          <t>461418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481465</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495972</t>
+          <t>496164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207079</t>
+          <t>206363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217254</t>
+          <t>217258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>695085</t>
+          <t>694030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711310</t>
+          <t>711395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393743</t>
+          <t>393380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400909</t>
+          <t>400911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217106</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615558</t>
+          <t>616155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624112</t>
+          <t>624086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302901</t>
+          <t>302583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312585</t>
+          <t>312578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140114</t>
+          <t>140705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445185</t>
+          <t>446228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456945</t>
+          <t>456948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167879</t>
+          <t>167750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177447</t>
+          <t>177321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73510</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242791</t>
+          <t>243043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252850</t>
+          <t>252878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3885</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125899</t>
+          <t>125660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154633</t>
+          <t>155306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>65493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72327</t>
+          <t>72348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81929</t>
+          <t>81610</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88861</t>
+          <t>88847</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1830185</t>
+          <t>1830279</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1855384</t>
+          <t>1854757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>878207</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>891055</t>
+          <t>891114</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2714772</t>
+          <t>2716877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2743223</t>
+          <t>2742994</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266237</t>
+          <t>265793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275986</t>
+          <t>275937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175424</t>
+          <t>175263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444944</t>
+          <t>445059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>455751</t>
+          <t>455966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448395</t>
+          <t>448711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>461276</t>
+          <t>461291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212437</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660240</t>
+          <t>661717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>673674</t>
+          <t>673705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18471</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408730</t>
+          <t>407845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421457</t>
+          <t>421473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239837</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241919</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650796</t>
+          <t>650875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663151</t>
+          <t>663609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>374480</t>
+          <t>375346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>389851</t>
+          <t>389706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588384</t>
+          <t>586826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>603081</t>
+          <t>603113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221001</t>
+          <t>221364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227681</t>
+          <t>227674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105959</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330514</t>
+          <t>330022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339038</t>
+          <t>339031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145183</t>
+          <t>144952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152460</t>
+          <t>152469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53590</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200943</t>
+          <t>200890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208401</t>
+          <t>208143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -5770,97 +5770,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83348</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56954</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31615</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1975281</t>
+          <t>1977526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2002579</t>
+          <t>2003172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1031376</t>
+          <t>1032149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1039548</t>
+          <t>1039552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3013073</t>
+          <t>3013548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3041170</t>
+          <t>3041517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241309</t>
+          <t>241110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249582</t>
+          <t>249588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164859</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166718</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407585</t>
+          <t>408907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>417267</t>
+          <t>416304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349281</t>
+          <t>349188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360264</t>
+          <t>360219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213934</t>
+          <t>213905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222102</t>
+          <t>222111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568031</t>
+          <t>568326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>581345</t>
+          <t>581185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416409</t>
+          <t>416305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426383</t>
+          <t>426375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663704</t>
+          <t>663925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673518</t>
+          <t>673609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>379811</t>
+          <t>378703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>388516</t>
+          <t>388513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>253511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261648</t>
+          <t>261646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>637294</t>
+          <t>636574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649110</t>
+          <t>649027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267523</t>
+          <t>266683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280320</t>
+          <t>279231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126519</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393207</t>
+          <t>393232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405724</t>
+          <t>405758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166456</t>
+          <t>166667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173724</t>
+          <t>173720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65516</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>234161</t>
+          <t>233640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241325</t>
+          <t>241315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,62 +8784,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6379</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6207</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87721</t>
+          <t>86769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123506</t>
+          <t>123334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,49 +9107,49 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2921</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13756</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>36</t>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1936628</t>
+          <t>1936115</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1958748</t>
+          <t>1959164</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,47 +9220,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1124004</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1117331</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1128119</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>98,86%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1124004</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1116458</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1127293</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3059406</t>
+          <t>3059512</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3083771</t>
+          <t>3083990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87378</t>
+          <t>88047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100682</t>
+          <t>100688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256434</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270573</t>
+          <t>270588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -10013,97 +10013,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4322</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4325</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137931</t>
+          <t>137734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368063</t>
+          <t>367120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273139</t>
+          <t>273323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281162</t>
+          <t>281154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146222</t>
+          <t>146440</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>422691</t>
+          <t>422138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>431187</t>
+          <t>431378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,47 +10749,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>8482</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335419</t>
+          <t>335705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343218</t>
+          <t>343257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191417</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,47 +10862,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>533512</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>528176</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>535672</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>533512</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>527767</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>535774</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249207</t>
+          <t>250600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259426</t>
+          <t>259929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129365</t>
+          <t>129368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134179</t>
+          <t>134119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381472</t>
+          <t>382050</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392148</t>
+          <t>392862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>183245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188810</t>
+          <t>188827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275879</t>
+          <t>275981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460513</t>
+          <t>459976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469066</t>
+          <t>468933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93839</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>99341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120428</t>
+          <t>120463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125817</t>
+          <t>125705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,82 +12086,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>18061</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>28069</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>18427</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>39892</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9252</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>18783</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>19245</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>40527</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1551949</t>
+          <t>1551770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1568189</t>
+          <t>1566723</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,82 +12199,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1018130</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1009321</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1023989</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2578684</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2566861</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2588326</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1018130</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1008599</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1023774</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2566226</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2587508</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265540</t>
+          <t>265383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277094</t>
+          <t>276981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178045</t>
+          <t>178253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>447038</t>
+          <t>448699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>461418</t>
+          <t>462012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482388</t>
+          <t>480286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496164</t>
+          <t>495382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217258</t>
+          <t>217264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694030</t>
+          <t>695558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711395</t>
+          <t>711734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>393415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400911</t>
+          <t>400925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218567</t>
+          <t>218248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616155</t>
+          <t>615228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624086</t>
+          <t>624105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302583</t>
+          <t>301689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312578</t>
+          <t>312583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140705</t>
+          <t>141042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446228</t>
+          <t>446155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456948</t>
+          <t>457570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167750</t>
+          <t>167135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177321</t>
+          <t>177380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243043</t>
+          <t>243253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252878</t>
+          <t>252860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>126041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155306</t>
+          <t>155327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65493</t>
+          <t>65752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72348</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81610</t>
+          <t>82442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88847</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1830279</t>
+          <t>1831175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1854757</t>
+          <t>1855502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>891114</t>
+          <t>890882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2716877</t>
+          <t>2716606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2742994</t>
+          <t>2743021</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265793</t>
+          <t>265303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275937</t>
+          <t>275576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175263</t>
+          <t>175820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445059</t>
+          <t>445472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>455966</t>
+          <t>455713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448711</t>
+          <t>449284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>461291</t>
+          <t>461263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661717</t>
+          <t>659880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>673705</t>
+          <t>673658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407845</t>
+          <t>407336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421473</t>
+          <t>421248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650875</t>
+          <t>649838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663609</t>
+          <t>663547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>375346</t>
+          <t>374376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>389706</t>
+          <t>388933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>586826</t>
+          <t>589145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>603113</t>
+          <t>603294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221364</t>
+          <t>221256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227674</t>
+          <t>227679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>105065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>330022</t>
+          <t>330374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339031</t>
+          <t>338903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144952</t>
+          <t>144978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152469</t>
+          <t>152482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200890</t>
+          <t>201044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208143</t>
+          <t>208149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,82 +6128,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>43958</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>31979</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>58695</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>43958</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>31268</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>59237</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1977526</t>
+          <t>1975868</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2003172</t>
+          <t>2001714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,82 +6241,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1037511</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1032399</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1039557</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>3028827</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>3014090</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3040806</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1037511</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1032149</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1039552</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3028827</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>3013548</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3041517</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241110</t>
+          <t>240954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249588</t>
+          <t>249593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>408907</t>
+          <t>408797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>416304</t>
+          <t>416298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349188</t>
+          <t>349809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360219</t>
+          <t>360273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213905</t>
+          <t>214991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222111</t>
+          <t>222113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568326</t>
+          <t>568174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>581185</t>
+          <t>581226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,82 +7377,82 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10674</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4421</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11096</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416305</t>
+          <t>416727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426375</t>
+          <t>426372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663925</t>
+          <t>663356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673609</t>
+          <t>673514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>378703</t>
+          <t>379878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253511</t>
+          <t>254015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261646</t>
+          <t>261643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636574</t>
+          <t>637210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649027</t>
+          <t>648992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>266683</t>
+          <t>266627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279231</t>
+          <t>279275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393232</t>
+          <t>392163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405758</t>
+          <t>405769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166667</t>
+          <t>165676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173720</t>
+          <t>173723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233640</t>
+          <t>234169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241315</t>
+          <t>241332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86769</t>
+          <t>86935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123334</t>
+          <t>124091</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1936115</t>
+          <t>1936766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1959164</t>
+          <t>1959032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1117331</t>
+          <t>1117917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3059512</t>
+          <t>3059483</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3083990</t>
+          <t>3084774</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96850</t>
+          <t>106663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>96533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100688</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>266752</t>
+          <t>272906</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>263141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270588</t>
+          <t>277425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>141396</t>
+          <t>152130</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137734</t>
+          <t>148533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,27 +10191,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>371531</t>
+          <t>401594</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367120</t>
+          <t>396457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,22 +10351,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -10396,12 +10396,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>278860</t>
+          <t>309319</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273323</t>
+          <t>302758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281154</t>
+          <t>311657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,27 +10499,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149561</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146440</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>428421</t>
+          <t>477972</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>422138</t>
+          <t>472244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>431378</t>
+          <t>481116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>282183</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>340958</t>
+          <t>349720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>335705</t>
+          <t>343752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343257</t>
+          <t>352626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>212704</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>533512</t>
+          <t>562424</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>528176</t>
+          <t>557369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535672</t>
+          <t>565545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>212704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>212704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192554</t>
+          <t>212704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>536658</t>
+          <t>566459</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>536658</t>
+          <t>566459</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>536658</t>
+          <t>566459</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>256110</t>
+          <t>273906</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250600</t>
+          <t>267003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259929</t>
+          <t>277392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>132470</t>
+          <t>145550</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129368</t>
+          <t>141877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134119</t>
+          <t>147322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>388580</t>
+          <t>419456</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382050</t>
+          <t>412140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392862</t>
+          <t>423756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>263014</t>
+          <t>280647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397771</t>
+          <t>428605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>186935</t>
+          <t>204681</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183245</t>
+          <t>201098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188827</t>
+          <t>206753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,27 +11528,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278949</t>
+          <t>79049</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275981</t>
+          <t>76767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465884</t>
+          <t>283730</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459976</t>
+          <t>279819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468933</t>
+          <t>286068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279399</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>469395</t>
+          <t>287382</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>103891</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>28532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>124004</t>
+          <t>137659</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120463</t>
+          <t>134264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125705</t>
+          <t>139614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126791</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,67 +12101,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>31502</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>21866</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>45461</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>18427</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>39892</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1560554</t>
+          <t>1660625</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1551770</t>
+          <t>1651422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1566723</t>
+          <t>1667328</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,67 +12214,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1018130</t>
+          <t>895115</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1009321</t>
+          <t>883200</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1023989</t>
+          <t>901687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2555740</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2541781</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2565376</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2566861</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2588326</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
